--- a/data/trans_orig/P24F-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P24F-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le gustaría dejar de fumar en 2007</t>
+          <t>Población según si le gustaría dejar de fumar en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>939</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>11503</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>973</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>8319</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13227</t>
+          <t>13656</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38054</t>
+          <t>37731</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58287</t>
+          <t>58673</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,47 +860,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>51,76%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>37183</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>28734</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>45555</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t>51,42%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>37183</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>28517</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>45966</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>51,42%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>71557</t>
+          <t>71054</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100022</t>
+          <t>99654</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,67%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38895</t>
+          <t>39353</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60660</t>
+          <t>61214</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15292</t>
+          <t>15671</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32117</t>
+          <t>31941</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>58943</t>
+          <t>59528</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86739</t>
+          <t>86350</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,51%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20381</t>
+          <t>18943</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16778</t>
+          <t>16769</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13009</t>
+          <t>12968</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30608</t>
+          <t>30979</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43770</t>
+          <t>44203</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68930</t>
+          <t>69194</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20230</t>
+          <t>20094</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39231</t>
+          <t>37871</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71341</t>
+          <t>69731</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101222</t>
+          <t>101379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,79%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60106</t>
+          <t>58964</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88940</t>
+          <t>88350</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45862</t>
+          <t>47276</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67826</t>
+          <t>68655</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111556</t>
+          <t>114403</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>148730</t>
+          <t>151876</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>49,13%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46861</t>
+          <t>46553</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>72764</t>
+          <t>73406</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22763</t>
+          <t>21542</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42776</t>
+          <t>41262</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>75670</t>
+          <t>76286</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>108023</t>
+          <t>107552</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15407</t>
+          <t>17278</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23169</t>
+          <t>22815</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15567</t>
+          <t>16025</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34782</t>
+          <t>35366</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>65075</t>
+          <t>65588</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>89022</t>
+          <t>89517</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26462</t>
+          <t>25697</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45472</t>
+          <t>44106</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>98195</t>
+          <t>97433</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>128617</t>
+          <t>128239</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,83%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28763</t>
+          <t>29426</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49658</t>
+          <t>50361</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19200</t>
+          <t>18829</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35253</t>
+          <t>35664</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52502</t>
+          <t>53526</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78497</t>
+          <t>80280</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>33,07%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>14809</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32466</t>
+          <t>33547</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10984</t>
+          <t>10937</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25399</t>
+          <t>25467</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30793</t>
+          <t>30650</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54350</t>
+          <t>55278</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>887</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8212</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15362</t>
+          <t>14885</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45686</t>
+          <t>45573</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70087</t>
+          <t>69370</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22098</t>
+          <t>21410</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39694</t>
+          <t>39688</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72828</t>
+          <t>73731</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>102172</t>
+          <t>104269</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,82%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>59566</t>
+          <t>60280</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>84908</t>
+          <t>85152</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49301</t>
+          <t>49970</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69156</t>
+          <t>69305</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>114986</t>
+          <t>114978</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>146004</t>
+          <t>148703</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,94%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25426</t>
+          <t>26845</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47755</t>
+          <t>48135</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19564</t>
+          <t>19489</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36012</t>
+          <t>36899</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61138</t>
+          <t>63364</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11159</t>
+          <t>10841</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>1776</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10713</t>
+          <t>10430</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20288</t>
+          <t>20737</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37597</t>
+          <t>38629</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18185</t>
+          <t>18266</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34198</t>
+          <t>33778</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43185</t>
+          <t>43535</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>66093</t>
+          <t>66137</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,97%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>27477</t>
+          <t>28395</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45481</t>
+          <t>46157</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18327</t>
+          <t>18870</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>33670</t>
+          <t>34019</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>50518</t>
+          <t>50355</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>73831</t>
+          <t>73969</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,42%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>8057</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>22601</t>
+          <t>22947</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>14618</t>
+          <t>14009</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>13765</t>
+          <t>13522</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>31352</t>
+          <t>30960</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10595</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>14363</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6872</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21505</t>
+          <t>22511</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>47791</t>
+          <t>46528</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>69351</t>
+          <t>68811</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30751</t>
+          <t>30679</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>68661</t>
+          <t>66866</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>95737</t>
+          <t>94274</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>42870</t>
+          <t>43242</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>64603</t>
+          <t>65044</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>20717</t>
+          <t>20829</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>36653</t>
+          <t>36643</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>69271</t>
+          <t>68834</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>95913</t>
+          <t>95306</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,07%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>16078</t>
+          <t>17001</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>11581</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8359</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>22773</t>
+          <t>23100</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15095</t>
+          <t>17224</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>13614</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>8710</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>24741</t>
+          <t>24035</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>92721</t>
+          <t>92229</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>123367</t>
+          <t>124236</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>50591</t>
+          <t>50739</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>76948</t>
+          <t>75836</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>152228</t>
+          <t>151481</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>191134</t>
+          <t>190200</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,09%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>69542</t>
+          <t>68042</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>98222</t>
+          <t>99463</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>56584</t>
+          <t>57891</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>82739</t>
+          <t>83792</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>134238</t>
+          <t>135726</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>172389</t>
+          <t>174010</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>44,0%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>24785</t>
+          <t>25218</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>46386</t>
+          <t>47770</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12921</t>
+          <t>13857</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>30077</t>
+          <t>31422</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>42123</t>
+          <t>41493</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>68676</t>
+          <t>70014</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -4715,12 +4715,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>12886</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>30834</t>
+          <t>32083</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>16879</t>
+          <t>17430</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>19417</t>
+          <t>19460</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>42271</t>
+          <t>42954</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>67909</t>
+          <t>67594</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>98691</t>
+          <t>98905</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>47230</t>
+          <t>45423</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>72750</t>
+          <t>71148</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>122357</t>
+          <t>123275</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>162075</t>
+          <t>163947</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4941,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>115840</t>
+          <t>114611</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>151879</t>
+          <t>150172</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>54465</t>
+          <t>55124</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>81697</t>
+          <t>80826</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>179128</t>
+          <t>178777</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>222767</t>
+          <t>223270</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>67277</t>
+          <t>68114</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>100071</t>
+          <t>98967</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>38612</t>
+          <t>37759</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>63322</t>
+          <t>62304</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>113679</t>
+          <t>114977</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>152763</t>
+          <t>155715</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>41959</t>
+          <t>43728</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>71914</t>
+          <t>72242</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>35269</t>
+          <t>36319</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>61706</t>
+          <t>62014</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>84722</t>
+          <t>85139</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>123624</t>
+          <t>123453</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>480607</t>
+          <t>480612</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>550754</t>
+          <t>552610</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>274323</t>
+          <t>276896</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>331182</t>
+          <t>330746</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>775717</t>
+          <t>775211</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>868448</t>
+          <t>864450</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>501939</t>
+          <t>505339</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>575240</t>
+          <t>578158</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>330293</t>
+          <t>329135</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>389451</t>
+          <t>387586</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>852732</t>
+          <t>851167</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>946516</t>
+          <t>944458</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,04%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>239529</t>
+          <t>239947</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>302795</t>
+          <t>301805</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>133553</t>
+          <t>131120</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>177637</t>
+          <t>175777</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>386331</t>
+          <t>390450</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>459901</t>
+          <t>462901</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le gustaría dejar de fumar en 2012</t>
+          <t>Población según si le gustaría dejar de fumar en 2012 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6089,12 +6089,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10821</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>10483</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16386</t>
+          <t>16057</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6174,12 +6174,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>8520</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26081</t>
+          <t>24475</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3372</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15903</t>
+          <t>15557</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14766</t>
+          <t>15172</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35052</t>
+          <t>35278</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91772</t>
+          <t>92542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113473</t>
+          <t>113373</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63615</t>
+          <t>63255</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>81569</t>
+          <t>81779</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>163174</t>
+          <t>163007</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>190015</t>
+          <t>190391</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,22%</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7364</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21309</t>
+          <t>21392</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6773</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>19612</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16742</t>
+          <t>17308</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36560</t>
+          <t>35937</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4924</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>947</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6743,12 +6743,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -6771,12 +6771,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18244</t>
+          <t>17872</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36001</t>
+          <t>37450</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6786,12 +6786,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18248</t>
+          <t>17388</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35923</t>
+          <t>36686</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40299</t>
+          <t>40607</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66369</t>
+          <t>67014</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>121249</t>
+          <t>120752</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>150080</t>
+          <t>148836</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74452</t>
+          <t>74385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99203</t>
+          <t>100606</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>203447</t>
+          <t>202964</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>242119</t>
+          <t>240749</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,43%</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30804</t>
+          <t>31356</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55971</t>
+          <t>56308</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24663</t>
+          <t>24147</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47134</t>
+          <t>47559</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>63988</t>
+          <t>63296</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>97014</t>
+          <t>97438</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>936</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9216</t>
+          <t>9477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -7340,12 +7340,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13221</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29392</t>
+          <t>29220</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7355,12 +7355,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21104</t>
+          <t>21912</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>22728</t>
+          <t>22479</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>44481</t>
+          <t>43576</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68810</t>
+          <t>68972</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90448</t>
+          <t>89865</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53340</t>
+          <t>53484</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71383</t>
+          <t>71651</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>129701</t>
+          <t>129604</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>157350</t>
+          <t>156700</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,06%</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17094</t>
+          <t>17393</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33993</t>
+          <t>34698</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18677</t>
+          <t>17278</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25030</t>
+          <t>25175</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46451</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4810</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7831,62 +7831,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5309</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5441</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -7909,12 +7909,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22252</t>
+          <t>22031</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42849</t>
+          <t>42038</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>7885</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21919</t>
+          <t>21557</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31447</t>
+          <t>32237</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>59232</t>
+          <t>57511</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7994,12 +7994,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>68137</t>
+          <t>68936</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>92280</t>
+          <t>92496</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>63043</t>
+          <t>63309</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>82666</t>
+          <t>82071</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140180</t>
+          <t>139774</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>170686</t>
+          <t>170280</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8107,12 +8107,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,04%</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10280</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26154</t>
+          <t>24859</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9315</t>
+          <t>9131</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24371</t>
+          <t>25126</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8185,12 +8185,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22516</t>
+          <t>22498</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44581</t>
+          <t>45044</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8220,12 +8220,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8385,7 +8385,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8400,62 +8400,62 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1927</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>5645</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>5635</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -8478,12 +8478,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12492</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29322</t>
+          <t>29157</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16280</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18614</t>
+          <t>18288</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39643</t>
+          <t>40052</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8563,12 +8563,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -8591,12 +8591,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>48356</t>
+          <t>47824</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>67466</t>
+          <t>67225</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33546</t>
+          <t>33819</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>49399</t>
+          <t>49724</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>87503</t>
+          <t>87466</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>112590</t>
+          <t>111800</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8676,12 +8676,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,28%</t>
         </is>
       </c>
     </row>
@@ -8704,12 +8704,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>21140</t>
+          <t>20601</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8719,12 +8719,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9575</t>
+          <t>9241</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>23520</t>
+          <t>23496</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>19524</t>
+          <t>19360</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>39826</t>
+          <t>38963</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -8939,7 +8939,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -9047,12 +9047,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12421</t>
+          <t>11011</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9062,12 +9062,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10828</t>
+          <t>11472</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9097,12 +9097,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18080</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>44065</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>62585</t>
+          <t>61728</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9175,12 +9175,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>42513</t>
+          <t>41513</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>56452</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>91956</t>
+          <t>92356</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>114884</t>
+          <t>114298</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>75,89%</t>
         </is>
       </c>
     </row>
@@ -9273,12 +9273,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>15865</t>
+          <t>16078</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>32284</t>
+          <t>31932</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9288,12 +9288,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>19398</t>
+          <t>18788</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>24603</t>
+          <t>25702</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>45509</t>
+          <t>46720</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9358,12 +9358,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>31,02%</t>
         </is>
       </c>
     </row>
@@ -9503,12 +9503,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12114</t>
+          <t>12911</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7094</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>15312</t>
+          <t>15202</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9588,12 +9588,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -9616,12 +9616,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>22540</t>
+          <t>22471</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>46815</t>
+          <t>45870</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>13408</t>
+          <t>13525</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>32828</t>
+          <t>31921</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>40862</t>
+          <t>41297</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>70110</t>
+          <t>70632</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9701,12 +9701,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -9729,12 +9729,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>143962</t>
+          <t>144225</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>179571</t>
+          <t>175943</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>97498</t>
+          <t>95649</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>125833</t>
+          <t>125657</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>249226</t>
+          <t>249462</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>295124</t>
+          <t>294589</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,62%</t>
         </is>
       </c>
     </row>
@@ -9842,12 +9842,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>62925</t>
+          <t>63575</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>93843</t>
+          <t>93024</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>44629</t>
+          <t>45146</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>70467</t>
+          <t>73825</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9892,12 +9892,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9912,12 +9912,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>115744</t>
+          <t>114316</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>157910</t>
+          <t>154976</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>32,94%</t>
         </is>
       </c>
     </row>
@@ -10072,12 +10072,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>12369</t>
+          <t>11647</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>972</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>15783</t>
+          <t>16085</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -10185,12 +10185,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>48194</t>
+          <t>48660</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>79409</t>
+          <t>78179</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10200,12 +10200,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>38934</t>
+          <t>38562</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>65230</t>
+          <t>64070</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10235,12 +10235,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>94121</t>
+          <t>93923</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>130836</t>
+          <t>132666</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -10298,12 +10298,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>139853</t>
+          <t>137929</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>172845</t>
+          <t>174036</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10313,12 +10313,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10333,12 +10333,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>95638</t>
+          <t>98078</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>127035</t>
+          <t>128151</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10348,12 +10348,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>242949</t>
+          <t>243841</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>288908</t>
+          <t>290517</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,64%</t>
         </is>
       </c>
     </row>
@@ -10411,12 +10411,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>58425</t>
+          <t>57511</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>88327</t>
+          <t>88394</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10446,12 +10446,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>30823</t>
+          <t>31100</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>56737</t>
+          <t>56219</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>95730</t>
+          <t>96861</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>135879</t>
+          <t>137337</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10496,12 +10496,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -10641,12 +10641,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>13914</t>
+          <t>13569</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>31575</t>
+          <t>33171</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10656,12 +10656,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10676,12 +10676,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>22705</t>
+          <t>22621</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10691,12 +10691,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>25232</t>
+          <t>25324</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>47798</t>
+          <t>50165</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -10754,12 +10754,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>186772</t>
+          <t>183707</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>242598</t>
+          <t>240272</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10789,12 +10789,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>120730</t>
+          <t>120235</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>168508</t>
+          <t>168334</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10804,12 +10804,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>323074</t>
+          <t>319727</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>394681</t>
+          <t>389484</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10839,12 +10839,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>789877</t>
+          <t>792481</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>863752</t>
+          <t>866741</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10902,12 +10902,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>583909</t>
+          <t>578231</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>646047</t>
+          <t>642317</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10917,12 +10917,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10937,12 +10937,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1395667</t>
+          <t>1393728</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1490237</t>
+          <t>1490702</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10952,12 +10952,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,23%</t>
         </is>
       </c>
     </row>
@@ -10980,12 +10980,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>253111</t>
+          <t>253796</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>314093</t>
+          <t>317323</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -10995,12 +10995,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11015,12 +11015,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>175560</t>
+          <t>177156</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>227924</t>
+          <t>229306</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11030,12 +11030,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11050,12 +11050,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>447121</t>
+          <t>447113</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>524307</t>
+          <t>526317</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le gustaría dejar de fumar en 2016</t>
+          <t>Población según si le gustaría dejar de fumar en 2016 (tasa de respuesta: 98,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>909</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -11559,12 +11559,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>17320</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34599</t>
+          <t>36950</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11574,12 +11574,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19843</t>
+          <t>19304</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11609,12 +11609,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11629,12 +11629,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27137</t>
+          <t>26155</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48977</t>
+          <t>49276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11644,12 +11644,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -11672,12 +11672,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55878</t>
+          <t>55862</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>76729</t>
+          <t>76791</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43436</t>
+          <t>43897</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59222</t>
+          <t>59191</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>104158</t>
+          <t>104579</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>130495</t>
+          <t>132388</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11757,12 +11757,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>73,87%</t>
         </is>
       </c>
     </row>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21364</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11800,12 +11800,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15815</t>
+          <t>14956</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30132</t>
+          <t>30554</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11870,12 +11870,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -12015,12 +12015,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11091</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12050,12 +12050,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12070,7 +12070,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12085,12 +12085,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12518</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -12128,12 +12128,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28220</t>
+          <t>28389</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52245</t>
+          <t>50757</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16160</t>
+          <t>16033</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35195</t>
+          <t>33661</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49382</t>
+          <t>48966</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78518</t>
+          <t>76940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12213,12 +12213,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -12241,12 +12241,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62220</t>
+          <t>60953</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89322</t>
+          <t>89245</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12256,12 +12256,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53329</t>
+          <t>51930</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75939</t>
+          <t>76040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12291,12 +12291,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>120651</t>
+          <t>121775</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>157795</t>
+          <t>159151</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12326,12 +12326,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,3%</t>
         </is>
       </c>
     </row>
@@ -12354,12 +12354,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>73328</t>
+          <t>74035</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103052</t>
+          <t>103089</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12369,12 +12369,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35791</t>
+          <t>35660</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58285</t>
+          <t>58788</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12404,12 +12404,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>117688</t>
+          <t>117271</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>154091</t>
+          <t>155601</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12439,12 +12439,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,27%</t>
         </is>
       </c>
     </row>
@@ -12584,12 +12584,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15216</t>
+          <t>13823</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>9099</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18852</t>
+          <t>19360</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12669,12 +12669,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -12697,12 +12697,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21304</t>
+          <t>21407</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12712,12 +12712,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10612</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12747,12 +12747,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>12894</t>
+          <t>12363</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>28430</t>
+          <t>28953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12782,12 +12782,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -12810,12 +12810,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48011</t>
+          <t>47576</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65782</t>
+          <t>66487</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48153</t>
+          <t>47331</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64000</t>
+          <t>63730</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12860,12 +12860,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100883</t>
+          <t>100669</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>125236</t>
+          <t>125417</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12895,12 +12895,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,76%</t>
         </is>
       </c>
     </row>
@@ -12923,12 +12923,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8065</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21887</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12938,12 +12938,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23531</t>
+          <t>24843</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12973,12 +12973,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20943</t>
+          <t>21762</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41402</t>
+          <t>40836</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13008,12 +13008,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -13153,12 +13153,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>10012</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9640</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13238,12 +13238,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -13266,12 +13266,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13860</t>
+          <t>13273</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32193</t>
+          <t>31172</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18289</t>
+          <t>18664</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36254</t>
+          <t>37926</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36652</t>
+          <t>37933</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>63214</t>
+          <t>64474</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13351,12 +13351,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -13379,12 +13379,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77778</t>
+          <t>77864</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>101403</t>
+          <t>101225</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13394,12 +13394,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>43007</t>
+          <t>44168</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64613</t>
+          <t>64652</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13429,12 +13429,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13449,12 +13449,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>127951</t>
+          <t>128921</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>160184</t>
+          <t>160322</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13464,12 +13464,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,63%</t>
         </is>
       </c>
     </row>
@@ -13492,12 +13492,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15266</t>
+          <t>15899</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33806</t>
+          <t>34198</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13507,12 +13507,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13527,12 +13527,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18792</t>
+          <t>18910</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37021</t>
+          <t>37063</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13542,12 +13542,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13562,12 +13562,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38311</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64382</t>
+          <t>64512</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13577,12 +13577,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -13722,12 +13722,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13757,12 +13757,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>820</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13792,12 +13792,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>813</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13807,12 +13807,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -13835,12 +13835,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14393</t>
+          <t>14041</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13870,12 +13870,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9806</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13905,12 +13905,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19375</t>
+          <t>19059</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13920,12 +13920,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -13948,12 +13948,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>46005</t>
+          <t>46496</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>63391</t>
+          <t>63376</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13983,12 +13983,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34455</t>
+          <t>35166</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>47351</t>
+          <t>47327</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14018,12 +14018,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>86165</t>
+          <t>86740</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>106849</t>
+          <t>108256</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14033,12 +14033,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>78,11%</t>
         </is>
       </c>
     </row>
@@ -14061,12 +14061,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>11989</t>
+          <t>11853</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>27498</t>
+          <t>27554</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14076,12 +14076,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14096,12 +14096,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3464</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>13409</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14111,12 +14111,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -14131,12 +14131,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>17669</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>35789</t>
+          <t>35603</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14146,12 +14146,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -14291,12 +14291,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>10885</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14326,12 +14326,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14361,12 +14361,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16094</t>
+          <t>16963</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -14404,12 +14404,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>17460</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14439,12 +14439,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8639</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22302</t>
+          <t>22758</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14474,12 +14474,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17517</t>
+          <t>17076</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>36437</t>
+          <t>35406</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14489,12 +14489,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -14517,12 +14517,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>49483</t>
+          <t>49830</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>66884</t>
+          <t>67658</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14552,12 +14552,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>31177</t>
+          <t>30515</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>48817</t>
+          <t>48159</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14587,12 +14587,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>86242</t>
+          <t>84864</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>110272</t>
+          <t>110974</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14602,12 +14602,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -14630,12 +14630,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7649</t>
+          <t>7615</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>21744</t>
+          <t>21341</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14665,12 +14665,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>7251</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>21283</t>
+          <t>22627</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>18545</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>38216</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -14860,12 +14860,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>9983</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14895,12 +14895,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>941</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14930,12 +14930,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>15625</t>
+          <t>15634</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -14973,12 +14973,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>52514</t>
+          <t>52313</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>80742</t>
+          <t>81693</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -15008,12 +15008,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>47261</t>
+          <t>46393</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>70766</t>
+          <t>70423</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -15043,12 +15043,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>106693</t>
+          <t>106625</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>143840</t>
+          <t>144464</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -15058,12 +15058,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,38%</t>
         </is>
       </c>
     </row>
@@ -15086,12 +15086,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>79219</t>
+          <t>77816</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>110314</t>
+          <t>109085</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15121,12 +15121,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>75823</t>
+          <t>76163</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>101228</t>
+          <t>102645</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>162040</t>
+          <t>164476</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>202342</t>
+          <t>202907</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,31%</t>
         </is>
       </c>
     </row>
@@ -15199,12 +15199,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>22005</t>
+          <t>21953</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>43208</t>
+          <t>43118</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -15234,12 +15234,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>13004</t>
+          <t>12713</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>29799</t>
+          <t>30960</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38563</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>65328</t>
+          <t>66119</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -15429,12 +15429,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>14846</t>
+          <t>15330</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -15444,12 +15444,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -15464,12 +15464,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>9551</t>
+          <t>9631</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -15479,12 +15479,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -15499,12 +15499,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>5667</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>20300</t>
+          <t>20578</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -15514,12 +15514,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -15542,12 +15542,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>34341</t>
+          <t>35334</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>60793</t>
+          <t>61622</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -15557,12 +15557,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -15577,12 +15577,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>26511</t>
+          <t>25694</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>48277</t>
+          <t>49035</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>66571</t>
+          <t>67543</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>99984</t>
+          <t>100745</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -15655,12 +15655,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>136198</t>
+          <t>133927</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>167228</t>
+          <t>166899</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -15670,12 +15670,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15690,12 +15690,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>110523</t>
+          <t>109805</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>139555</t>
+          <t>138741</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>256179</t>
+          <t>255281</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>298033</t>
+          <t>298534</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,15%</t>
         </is>
       </c>
     </row>
@@ -15768,12 +15768,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>37413</t>
+          <t>37395</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>64078</t>
+          <t>63989</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15783,12 +15783,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15803,12 +15803,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>34884</t>
+          <t>34056</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>59543</t>
+          <t>58814</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>78733</t>
+          <t>78319</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>113473</t>
+          <t>112577</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -15998,12 +15998,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>22930</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>46452</t>
+          <t>46625</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -16013,12 +16013,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>14646</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>42513</t>
+          <t>42262</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>72600</t>
+          <t>71243</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -16111,12 +16111,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>199312</t>
+          <t>204103</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>259409</t>
+          <t>260841</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -16126,12 +16126,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -16146,12 +16146,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>158616</t>
+          <t>159086</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>208637</t>
+          <t>208274</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>374471</t>
+          <t>374979</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>452268</t>
+          <t>449093</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>614349</t>
+          <t>612150</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>682997</t>
+          <t>681503</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -16239,12 +16239,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16259,12 +16259,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>491422</t>
+          <t>491200</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>551755</t>
+          <t>551729</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1128989</t>
+          <t>1122715</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1218215</t>
+          <t>1214632</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,49%</t>
         </is>
       </c>
     </row>
@@ -16337,12 +16337,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>222344</t>
+          <t>219290</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>277521</t>
+          <t>280960</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -16352,12 +16352,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -16372,12 +16372,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>159466</t>
+          <t>162480</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>212258</t>
+          <t>210310</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -16387,12 +16387,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -16407,12 +16407,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>397162</t>
+          <t>400894</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>473711</t>
+          <t>476394</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -16422,12 +16422,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24F-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P24F-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>923</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11503</t>
+          <t>9820</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>987</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8319</t>
+          <t>8115</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13656</t>
+          <t>13889</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37731</t>
+          <t>37896</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58673</t>
+          <t>59406</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28734</t>
+          <t>29055</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45555</t>
+          <t>47076</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>71054</t>
+          <t>72793</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99654</t>
+          <t>100232</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,98%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39353</t>
+          <t>38524</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>61214</t>
+          <t>60755</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15671</t>
+          <t>15623</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31941</t>
+          <t>31931</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>59528</t>
+          <t>59995</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86350</t>
+          <t>86086</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,37%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6496</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18943</t>
+          <t>19757</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16769</t>
+          <t>16425</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12968</t>
+          <t>13617</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30979</t>
+          <t>31316</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>4856</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44203</t>
+          <t>44623</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69194</t>
+          <t>70446</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20094</t>
+          <t>21010</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37871</t>
+          <t>40422</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69731</t>
+          <t>69492</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101379</t>
+          <t>102427</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58964</t>
+          <t>60143</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88350</t>
+          <t>88407</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47276</t>
+          <t>46702</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68655</t>
+          <t>68286</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>114403</t>
+          <t>113932</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>151876</t>
+          <t>146889</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>47,51%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46553</t>
+          <t>47066</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73406</t>
+          <t>72308</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21542</t>
+          <t>22583</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41262</t>
+          <t>41391</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>76286</t>
+          <t>76213</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>107552</t>
+          <t>108914</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17278</t>
+          <t>16280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>9022</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22815</t>
+          <t>22875</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16025</t>
+          <t>15491</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35366</t>
+          <t>34835</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>65588</t>
+          <t>64971</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>89517</t>
+          <t>90440</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25697</t>
+          <t>26622</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44106</t>
+          <t>44564</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>97433</t>
+          <t>96785</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>128239</t>
+          <t>127753</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,63%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29426</t>
+          <t>28965</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50361</t>
+          <t>50098</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>19258</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35664</t>
+          <t>35366</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53526</t>
+          <t>53382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80280</t>
+          <t>80350</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,1%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14809</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33547</t>
+          <t>32777</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>10897</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25467</t>
+          <t>25824</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30650</t>
+          <t>29694</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55278</t>
+          <t>52790</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1699</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>10232</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>944</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14885</t>
+          <t>14594</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45573</t>
+          <t>45284</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>69370</t>
+          <t>69504</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21410</t>
+          <t>21968</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39688</t>
+          <t>40252</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>73731</t>
+          <t>72476</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>104269</t>
+          <t>103596</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,57%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60280</t>
+          <t>59875</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>85152</t>
+          <t>86695</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49970</t>
+          <t>49434</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69305</t>
+          <t>68683</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>114978</t>
+          <t>114411</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>148703</t>
+          <t>148398</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,82%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26845</t>
+          <t>25523</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48135</t>
+          <t>47708</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>6872</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19489</t>
+          <t>19607</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36899</t>
+          <t>36108</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63364</t>
+          <t>61272</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10841</t>
+          <t>10132</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10430</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>20194</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38629</t>
+          <t>37676</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18266</t>
+          <t>18873</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33778</t>
+          <t>33844</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43535</t>
+          <t>43479</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>66137</t>
+          <t>66734</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,39%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>28395</t>
+          <t>27124</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46157</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18870</t>
+          <t>18901</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34019</t>
+          <t>33714</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>50355</t>
+          <t>50253</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>73969</t>
+          <t>74532</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,81%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>22947</t>
+          <t>22346</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>14009</t>
+          <t>13445</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>13522</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>30960</t>
+          <t>32402</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14363</t>
+          <t>14682</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22511</t>
+          <t>21169</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>46528</t>
+          <t>47010</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>68811</t>
+          <t>68613</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>16188</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30679</t>
+          <t>31516</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>66866</t>
+          <t>68184</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>94274</t>
+          <t>94933</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,88%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>43242</t>
+          <t>43088</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>65044</t>
+          <t>65165</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>20829</t>
+          <t>20013</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>36643</t>
+          <t>36167</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>68834</t>
+          <t>68604</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>95306</t>
+          <t>96197</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,54%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>16614</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11581</t>
+          <t>11482</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>23100</t>
+          <t>23582</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>17224</t>
+          <t>15631</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2893</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13614</t>
+          <t>13555</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>8501</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>24035</t>
+          <t>23815</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>92229</t>
+          <t>92780</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>124236</t>
+          <t>124845</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>50739</t>
+          <t>51901</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>75836</t>
+          <t>76986</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>151481</t>
+          <t>152357</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>190200</t>
+          <t>191686</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,47%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>68042</t>
+          <t>68862</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>99463</t>
+          <t>98524</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>57891</t>
+          <t>56602</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>83792</t>
+          <t>82684</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>135726</t>
+          <t>133912</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>174010</t>
+          <t>173377</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,84%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>25218</t>
+          <t>24772</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>47770</t>
+          <t>46198</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>13857</t>
+          <t>13345</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>31422</t>
+          <t>32382</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>41493</t>
+          <t>42779</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>70014</t>
+          <t>73229</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -4715,12 +4715,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>12836</t>
+          <t>12526</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>32083</t>
+          <t>31313</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>17430</t>
+          <t>16898</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>19460</t>
+          <t>19377</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>42954</t>
+          <t>42420</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>67594</t>
+          <t>68331</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>98905</t>
+          <t>99822</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>45423</t>
+          <t>46923</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>71148</t>
+          <t>72008</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>123275</t>
+          <t>120769</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>163947</t>
+          <t>161818</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4941,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>114611</t>
+          <t>113835</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>150172</t>
+          <t>149916</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>55124</t>
+          <t>55755</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>80826</t>
+          <t>82009</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>178777</t>
+          <t>179176</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>223270</t>
+          <t>223111</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,28%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>68114</t>
+          <t>68485</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>98967</t>
+          <t>100036</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>37759</t>
+          <t>37861</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>62304</t>
+          <t>63275</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>114977</t>
+          <t>113091</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>155715</t>
+          <t>151061</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>43728</t>
+          <t>42325</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>72242</t>
+          <t>72463</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>36319</t>
+          <t>34837</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>62014</t>
+          <t>61009</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>85139</t>
+          <t>85318</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>123453</t>
+          <t>125985</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>480612</t>
+          <t>481172</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>552610</t>
+          <t>555753</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>276896</t>
+          <t>272821</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>330746</t>
+          <t>329354</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>775211</t>
+          <t>775466</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>864450</t>
+          <t>866010</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>505339</t>
+          <t>503800</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>578158</t>
+          <t>577745</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>329135</t>
+          <t>329903</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>387586</t>
+          <t>387843</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>851167</t>
+          <t>854570</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>944458</t>
+          <t>950365</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>239947</t>
+          <t>240708</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>301805</t>
+          <t>300911</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>131120</t>
+          <t>132167</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>175777</t>
+          <t>177644</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>390450</t>
+          <t>387870</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>462901</t>
+          <t>463161</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -6089,12 +6089,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10218</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16057</t>
+          <t>16669</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6174,12 +6174,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24475</t>
+          <t>24423</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15557</t>
+          <t>15164</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15172</t>
+          <t>14412</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35278</t>
+          <t>34139</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92542</t>
+          <t>93013</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113373</t>
+          <t>113621</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63255</t>
+          <t>63552</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>81779</t>
+          <t>81444</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>163007</t>
+          <t>164070</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>190391</t>
+          <t>190303</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7364</t>
+          <t>7366</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21392</t>
+          <t>20506</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19612</t>
+          <t>19792</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17308</t>
+          <t>17576</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>36467</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>933</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>8830</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6743,12 +6743,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -6771,12 +6771,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17872</t>
+          <t>17513</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37450</t>
+          <t>35986</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6786,12 +6786,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17388</t>
+          <t>18245</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36686</t>
+          <t>36015</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40607</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67014</t>
+          <t>66559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120752</t>
+          <t>118870</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148836</t>
+          <t>148870</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74385</t>
+          <t>75017</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>100606</t>
+          <t>100972</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>202964</t>
+          <t>201742</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>240749</t>
+          <t>241147</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,54%</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31356</t>
+          <t>33079</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56308</t>
+          <t>58641</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24147</t>
+          <t>24756</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47559</t>
+          <t>48686</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>63296</t>
+          <t>61460</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>97438</t>
+          <t>97761</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,38%</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>931</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9477</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7312,12 +7312,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -7340,12 +7340,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>12430</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29220</t>
+          <t>29883</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7355,12 +7355,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6277</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21912</t>
+          <t>20469</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>22479</t>
+          <t>22676</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>43576</t>
+          <t>45532</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68972</t>
+          <t>68079</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89865</t>
+          <t>90002</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53484</t>
+          <t>54102</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71651</t>
+          <t>71541</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>129604</t>
+          <t>129352</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>156700</t>
+          <t>158586</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,94%</t>
         </is>
       </c>
     </row>
@@ -7566,49 +7566,49 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>17245</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>34265</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>19,78%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>13,57%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>26,97%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>10225</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>5139</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
           <t>17393</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>34698</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>19,78%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>27,31%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>10225</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>5036</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>17278</t>
-        </is>
-      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>11,69%</t>
@@ -7616,12 +7616,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25175</t>
+          <t>24568</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>46715</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>4770</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -7909,12 +7909,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22031</t>
+          <t>20898</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42038</t>
+          <t>41767</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7885</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21557</t>
+          <t>21763</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32237</t>
+          <t>33021</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>57511</t>
+          <t>57664</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7994,12 +7994,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>68936</t>
+          <t>68935</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>92496</t>
+          <t>92356</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>63309</t>
+          <t>63869</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>82071</t>
+          <t>82521</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>139774</t>
+          <t>139207</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>170280</t>
+          <t>168951</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8107,12 +8107,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,47%</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9957</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24859</t>
+          <t>25239</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9131</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25126</t>
+          <t>24823</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8185,12 +8185,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22498</t>
+          <t>22974</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45044</t>
+          <t>44804</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8220,12 +8220,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8385,7 +8385,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5645</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -8478,12 +8478,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>12269</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29157</t>
+          <t>29436</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14929</t>
+          <t>15710</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18288</t>
+          <t>18012</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40052</t>
+          <t>39419</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8563,12 +8563,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -8591,12 +8591,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>47824</t>
+          <t>46972</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>67225</t>
+          <t>66642</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33819</t>
+          <t>33377</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>49724</t>
+          <t>48938</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>87466</t>
+          <t>86555</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>111800</t>
+          <t>112309</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8676,12 +8676,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,61%</t>
         </is>
       </c>
     </row>
@@ -8704,12 +8704,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7177</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20601</t>
+          <t>20825</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8719,12 +8719,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9241</t>
+          <t>9263</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>23496</t>
+          <t>23252</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>19360</t>
+          <t>19590</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>38963</t>
+          <t>39328</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,08%</t>
         </is>
       </c>
     </row>
@@ -8939,7 +8939,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -9047,12 +9047,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>11795</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9062,12 +9062,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11472</t>
+          <t>10036</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9097,12 +9097,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>17252</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>44065</t>
+          <t>44800</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>61728</t>
+          <t>62474</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9175,12 +9175,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>41513</t>
+          <t>42562</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>56452</t>
+          <t>56556</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>92356</t>
+          <t>91911</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>114298</t>
+          <t>114601</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>76,09%</t>
         </is>
       </c>
     </row>
@@ -9273,12 +9273,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>16078</t>
+          <t>15589</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>31932</t>
+          <t>32204</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9288,12 +9288,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>18788</t>
+          <t>18707</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>25702</t>
+          <t>25290</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>46720</t>
+          <t>46171</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9358,12 +9358,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -9503,12 +9503,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12911</t>
+          <t>12134</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>15202</t>
+          <t>15645</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9588,12 +9588,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -9616,12 +9616,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>22471</t>
+          <t>21955</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>45870</t>
+          <t>45112</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>13525</t>
+          <t>12998</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>31921</t>
+          <t>32016</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>41297</t>
+          <t>40108</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>70632</t>
+          <t>70766</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9701,12 +9701,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -9729,12 +9729,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>144225</t>
+          <t>143750</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>175943</t>
+          <t>178893</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>95649</t>
+          <t>94559</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>125657</t>
+          <t>122894</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>249462</t>
+          <t>248908</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>294589</t>
+          <t>293830</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,46%</t>
         </is>
       </c>
     </row>
@@ -9842,12 +9842,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>63575</t>
+          <t>62554</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>93024</t>
+          <t>95927</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>45146</t>
+          <t>44766</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>73825</t>
+          <t>71888</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9892,12 +9892,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9912,12 +9912,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>114316</t>
+          <t>116025</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>154976</t>
+          <t>157840</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,55%</t>
         </is>
       </c>
     </row>
@@ -10072,12 +10072,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>11647</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10087,12 +10087,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>961</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>8173</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>16085</t>
+          <t>16071</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -10185,12 +10185,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>48660</t>
+          <t>49200</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>78179</t>
+          <t>75824</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10200,12 +10200,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>38562</t>
+          <t>39472</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>64070</t>
+          <t>64953</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10235,12 +10235,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>93923</t>
+          <t>94429</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>132666</t>
+          <t>133309</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,45%</t>
         </is>
       </c>
     </row>
@@ -10298,12 +10298,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>137929</t>
+          <t>137734</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>174036</t>
+          <t>172242</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10313,12 +10313,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10333,12 +10333,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>98078</t>
+          <t>94305</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>128151</t>
+          <t>125293</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10348,12 +10348,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>243841</t>
+          <t>244443</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>290517</t>
+          <t>292368</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -10411,12 +10411,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>57511</t>
+          <t>58031</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>88394</t>
+          <t>89055</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10446,12 +10446,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>31100</t>
+          <t>31257</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>56219</t>
+          <t>55917</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>96861</t>
+          <t>96311</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>137337</t>
+          <t>135726</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10496,12 +10496,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -10641,12 +10641,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>13569</t>
+          <t>13874</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>33171</t>
+          <t>33475</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10656,12 +10656,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10676,12 +10676,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>22621</t>
+          <t>22927</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10691,12 +10691,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>25324</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>50165</t>
+          <t>48169</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -10754,12 +10754,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>183707</t>
+          <t>185735</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>240272</t>
+          <t>240356</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10789,12 +10789,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>120235</t>
+          <t>121677</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>168334</t>
+          <t>167330</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10804,12 +10804,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>319727</t>
+          <t>319466</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>389484</t>
+          <t>392662</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10839,12 +10839,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>792481</t>
+          <t>792612</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>866741</t>
+          <t>867469</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10887,7 +10887,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10902,12 +10902,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>578231</t>
+          <t>581987</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>642317</t>
+          <t>644571</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10917,12 +10917,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10937,12 +10937,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1393728</t>
+          <t>1390516</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1490702</t>
+          <t>1486904</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10952,12 +10952,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,06%</t>
         </is>
       </c>
     </row>
@@ -10980,12 +10980,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>253796</t>
+          <t>254205</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>317323</t>
+          <t>314631</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -10995,12 +10995,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11015,12 +11015,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>177156</t>
+          <t>176116</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>229306</t>
+          <t>230053</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11030,12 +11030,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11050,12 +11050,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>447113</t>
+          <t>448551</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>526317</t>
+          <t>533812</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11065,12 +11065,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>6192</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>924</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7915</t>
+          <t>8755</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -11559,12 +11559,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17320</t>
+          <t>16404</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36950</t>
+          <t>36434</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11574,12 +11574,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>6817</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19304</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11609,12 +11609,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11629,12 +11629,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26155</t>
+          <t>26841</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49276</t>
+          <t>49407</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11644,12 +11644,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -11672,12 +11672,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55862</t>
+          <t>54898</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>76791</t>
+          <t>76570</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43897</t>
+          <t>43785</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59191</t>
+          <t>59015</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>104579</t>
+          <t>105617</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>132388</t>
+          <t>131533</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11757,12 +11757,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,4%</t>
         </is>
       </c>
     </row>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6457</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20894</t>
+          <t>20589</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11800,12 +11800,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14956</t>
+          <t>15591</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>12212</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30554</t>
+          <t>30491</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11870,12 +11870,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -12015,12 +12015,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12035,7 +12035,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12050,12 +12050,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12070,7 +12070,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12085,12 +12085,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>13009</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -12128,12 +12128,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28389</t>
+          <t>28613</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50757</t>
+          <t>52942</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16033</t>
+          <t>17045</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33661</t>
+          <t>33937</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48966</t>
+          <t>49319</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76940</t>
+          <t>77135</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12213,12 +12213,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -12241,12 +12241,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60953</t>
+          <t>61145</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89245</t>
+          <t>90002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12256,12 +12256,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51930</t>
+          <t>51342</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76040</t>
+          <t>76257</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12291,12 +12291,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121775</t>
+          <t>121462</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>159151</t>
+          <t>158990</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12326,12 +12326,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,25%</t>
         </is>
       </c>
     </row>
@@ -12354,12 +12354,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74035</t>
+          <t>72740</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103089</t>
+          <t>103058</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12369,12 +12369,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35660</t>
+          <t>36103</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58788</t>
+          <t>59269</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12404,12 +12404,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>117271</t>
+          <t>119506</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>155601</t>
+          <t>154104</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12439,12 +12439,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>44,83%</t>
         </is>
       </c>
     </row>
@@ -12584,12 +12584,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13823</t>
+          <t>14017</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>913</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9099</t>
+          <t>9286</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19360</t>
+          <t>18994</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12669,12 +12669,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -12697,12 +12697,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8533</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21407</t>
+          <t>21908</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12712,12 +12712,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12747,12 +12747,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>12363</t>
+          <t>12850</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>28953</t>
+          <t>28591</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12782,12 +12782,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -12810,12 +12810,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47576</t>
+          <t>48281</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66487</t>
+          <t>66216</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47331</t>
+          <t>47794</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63730</t>
+          <t>64285</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12860,12 +12860,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100669</t>
+          <t>100505</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>125417</t>
+          <t>125325</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12895,12 +12895,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,71%</t>
         </is>
       </c>
     </row>
@@ -12923,12 +12923,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8598</t>
+          <t>8413</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>22041</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12938,12 +12938,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24843</t>
+          <t>23166</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12973,12 +12973,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21762</t>
+          <t>21445</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40836</t>
+          <t>40158</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13008,12 +13008,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -13153,12 +13153,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10012</t>
+          <t>9536</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>9739</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -13266,12 +13266,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13273</t>
+          <t>13752</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31172</t>
+          <t>31931</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>18688</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37926</t>
+          <t>37821</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>37933</t>
+          <t>37495</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>64474</t>
+          <t>63013</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13351,12 +13351,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -13379,12 +13379,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77864</t>
+          <t>76693</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>101225</t>
+          <t>101635</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13394,12 +13394,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44168</t>
+          <t>44103</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64652</t>
+          <t>67118</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13429,12 +13429,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13449,12 +13449,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>128921</t>
+          <t>128143</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>160322</t>
+          <t>159463</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13464,12 +13464,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,29%</t>
         </is>
       </c>
     </row>
@@ -13492,12 +13492,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15899</t>
+          <t>14559</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34198</t>
+          <t>34590</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13507,12 +13507,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13527,12 +13527,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18910</t>
+          <t>17571</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37063</t>
+          <t>36781</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13542,12 +13542,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13562,12 +13562,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38311</t>
+          <t>39453</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64512</t>
+          <t>65930</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13577,12 +13577,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -13757,12 +13757,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>7885</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13777,7 +13777,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13792,12 +13792,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>817</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13812,7 +13812,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -13835,12 +13835,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14041</t>
+          <t>13848</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13870,12 +13870,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10690</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13905,12 +13905,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19059</t>
+          <t>20370</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13920,12 +13920,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -13948,12 +13948,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>46496</t>
+          <t>46890</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>63376</t>
+          <t>63719</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13983,12 +13983,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>35166</t>
+          <t>34658</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>47327</t>
+          <t>47535</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14018,12 +14018,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>86740</t>
+          <t>85734</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>108256</t>
+          <t>107248</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14033,12 +14033,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,38%</t>
         </is>
       </c>
     </row>
@@ -14061,12 +14061,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>27554</t>
+          <t>27662</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14076,12 +14076,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14096,12 +14096,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3547</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13409</t>
+          <t>13467</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14116,7 +14116,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -14131,12 +14131,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>17329</t>
+          <t>18048</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>35603</t>
+          <t>37899</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14146,12 +14146,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>27,34%</t>
         </is>
       </c>
     </row>
@@ -14291,12 +14291,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10885</t>
+          <t>11205</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14326,12 +14326,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14361,12 +14361,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16963</t>
+          <t>16130</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -14404,12 +14404,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17460</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14439,12 +14439,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22758</t>
+          <t>23561</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14474,12 +14474,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>16716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>35406</t>
+          <t>35874</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14489,12 +14489,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -14517,12 +14517,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>49830</t>
+          <t>48992</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>67658</t>
+          <t>67128</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14552,12 +14552,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>30515</t>
+          <t>30749</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>48159</t>
+          <t>47894</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14587,12 +14587,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>84864</t>
+          <t>85589</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>110974</t>
+          <t>110539</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14602,12 +14602,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,04%</t>
         </is>
       </c>
     </row>
@@ -14630,12 +14630,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>21341</t>
+          <t>22588</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14665,12 +14665,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7251</t>
+          <t>7849</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>22627</t>
+          <t>22443</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>19002</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>38216</t>
+          <t>38605</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -14860,12 +14860,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9983</t>
+          <t>10593</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14895,12 +14895,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>924</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14930,12 +14930,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>15634</t>
+          <t>16535</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14945,12 +14945,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -14973,12 +14973,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>52313</t>
+          <t>53573</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>81693</t>
+          <t>81645</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -15008,12 +15008,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>46393</t>
+          <t>47227</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>70423</t>
+          <t>71128</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -15043,12 +15043,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>106625</t>
+          <t>103822</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>144464</t>
+          <t>142895</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -15058,12 +15058,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,95%</t>
         </is>
       </c>
     </row>
@@ -15086,12 +15086,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>77816</t>
+          <t>78360</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>109085</t>
+          <t>109435</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15121,12 +15121,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>76163</t>
+          <t>75514</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>102645</t>
+          <t>102111</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>164476</t>
+          <t>162506</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>202907</t>
+          <t>203045</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,35%</t>
         </is>
       </c>
     </row>
@@ -15199,12 +15199,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>21953</t>
+          <t>21430</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>43118</t>
+          <t>42119</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -15234,12 +15234,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12713</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>30960</t>
+          <t>29071</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>38563</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>66119</t>
+          <t>65514</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -15429,12 +15429,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>15330</t>
+          <t>15428</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -15444,12 +15444,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -15464,12 +15464,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>991</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>9631</t>
+          <t>9433</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -15479,12 +15479,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -15499,12 +15499,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>5667</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>20578</t>
+          <t>20717</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -15514,12 +15514,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -15542,12 +15542,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>35334</t>
+          <t>34063</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>61622</t>
+          <t>60362</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -15557,12 +15557,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -15577,12 +15577,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>25694</t>
+          <t>26342</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>49035</t>
+          <t>47732</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>67543</t>
+          <t>66284</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>100745</t>
+          <t>99304</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>
@@ -15655,12 +15655,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>133927</t>
+          <t>133939</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>166899</t>
+          <t>166309</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -15670,12 +15670,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15690,12 +15690,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>109805</t>
+          <t>109960</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>138741</t>
+          <t>139742</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>255281</t>
+          <t>254139</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>298534</t>
+          <t>297532</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>63,94%</t>
         </is>
       </c>
     </row>
@@ -15768,12 +15768,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>37395</t>
+          <t>37464</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>63989</t>
+          <t>64582</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15783,12 +15783,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15803,12 +15803,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>34056</t>
+          <t>35049</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>58814</t>
+          <t>60746</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>78319</t>
+          <t>79102</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>112577</t>
+          <t>113674</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -15998,12 +15998,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>22748</t>
+          <t>23438</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>46625</t>
+          <t>46624</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>14646</t>
+          <t>15834</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>33681</t>
+          <t>34599</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>42262</t>
+          <t>43597</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>71243</t>
+          <t>73105</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -16111,12 +16111,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>204103</t>
+          <t>201590</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>260841</t>
+          <t>259692</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -16126,12 +16126,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -16146,12 +16146,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>159086</t>
+          <t>160201</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>208035</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>374979</t>
+          <t>372805</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>449093</t>
+          <t>448824</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>612150</t>
+          <t>611752</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>681503</t>
+          <t>683084</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -16239,12 +16239,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16259,12 +16259,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>491200</t>
+          <t>490928</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>551729</t>
+          <t>552543</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1122715</t>
+          <t>1126482</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1214632</t>
+          <t>1219628</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,73%</t>
         </is>
       </c>
     </row>
@@ -16337,12 +16337,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>219290</t>
+          <t>223984</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>280960</t>
+          <t>278454</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -16352,12 +16352,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -16372,12 +16372,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>162480</t>
+          <t>159183</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>210310</t>
+          <t>211036</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -16387,12 +16387,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -16407,12 +16407,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>400894</t>
+          <t>398439</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>476394</t>
+          <t>480744</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -16422,12 +16422,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
